--- a/artfynd/A 49689-2023 artfynd.xlsx
+++ b/artfynd/A 49689-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113201184</v>
       </c>
       <c r="B2" t="n">
-        <v>91290</v>
+        <v>91306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113201517</v>
+        <v>113201732</v>
       </c>
       <c r="B3" t="n">
-        <v>91290</v>
+        <v>96277</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338715</v>
+        <v>338771</v>
       </c>
       <c r="R3" t="n">
-        <v>6560995</v>
+        <v>6560994</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113201732</v>
+        <v>113201517</v>
       </c>
       <c r="B4" t="n">
-        <v>96261</v>
+        <v>91306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338771</v>
+        <v>338715</v>
       </c>
       <c r="R4" t="n">
-        <v>6560994</v>
+        <v>6560995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 49689-2023 artfynd.xlsx
+++ b/artfynd/A 49689-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113201184</v>
+        <v>113201732</v>
       </c>
       <c r="B2" t="n">
-        <v>91306</v>
+        <v>96277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338431</v>
+        <v>338771</v>
       </c>
       <c r="R2" t="n">
-        <v>6560810</v>
+        <v>6560994</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113201732</v>
+        <v>113201184</v>
       </c>
       <c r="B3" t="n">
-        <v>96277</v>
+        <v>91306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338771</v>
+        <v>338431</v>
       </c>
       <c r="R3" t="n">
-        <v>6560994</v>
+        <v>6560810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49689-2023 artfynd.xlsx
+++ b/artfynd/A 49689-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113201732</v>
+        <v>113201517</v>
       </c>
       <c r="B2" t="n">
-        <v>96277</v>
+        <v>91306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338771</v>
+        <v>338715</v>
       </c>
       <c r="R2" t="n">
-        <v>6560994</v>
+        <v>6560995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113201184</v>
+        <v>113201732</v>
       </c>
       <c r="B3" t="n">
-        <v>91306</v>
+        <v>96277</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338431</v>
+        <v>338771</v>
       </c>
       <c r="R3" t="n">
-        <v>6560810</v>
+        <v>6560994</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113201517</v>
+        <v>113201184</v>
       </c>
       <c r="B4" t="n">
         <v>91306</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338715</v>
+        <v>338431</v>
       </c>
       <c r="R4" t="n">
-        <v>6560995</v>
+        <v>6560810</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 49689-2023 artfynd.xlsx
+++ b/artfynd/A 49689-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113201517</v>
       </c>
       <c r="B2" t="n">
-        <v>91306</v>
+        <v>91318</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113201732</v>
+        <v>113201184</v>
       </c>
       <c r="B3" t="n">
-        <v>96277</v>
+        <v>91318</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338771</v>
+        <v>338431</v>
       </c>
       <c r="R3" t="n">
-        <v>6560994</v>
+        <v>6560810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113201184</v>
+        <v>113201732</v>
       </c>
       <c r="B4" t="n">
-        <v>91306</v>
+        <v>96289</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338431</v>
+        <v>338771</v>
       </c>
       <c r="R4" t="n">
-        <v>6560810</v>
+        <v>6560994</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 49689-2023 artfynd.xlsx
+++ b/artfynd/A 49689-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113201517</v>
+        <v>113201184</v>
       </c>
       <c r="B2" t="n">
         <v>91318</v>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338715</v>
+        <v>338431</v>
       </c>
       <c r="R2" t="n">
-        <v>6560995</v>
+        <v>6560810</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +788,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113201184</v>
+        <v>113201517</v>
       </c>
       <c r="B3" t="n">
         <v>91318</v>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338431</v>
+        <v>338715</v>
       </c>
       <c r="R3" t="n">
-        <v>6560810</v>
+        <v>6560995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49689-2023 artfynd.xlsx
+++ b/artfynd/A 49689-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113201184</v>
+        <v>113201517</v>
       </c>
       <c r="B2" t="n">
-        <v>91318</v>
+        <v>91340</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338431</v>
+        <v>338715</v>
       </c>
       <c r="R2" t="n">
-        <v>6560810</v>
+        <v>6560995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113201517</v>
+        <v>113201184</v>
       </c>
       <c r="B3" t="n">
-        <v>91318</v>
+        <v>91340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338715</v>
+        <v>338431</v>
       </c>
       <c r="R3" t="n">
-        <v>6560995</v>
+        <v>6560810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
         <v>113201732</v>
       </c>
       <c r="B4" t="n">
-        <v>96289</v>
+        <v>96311</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 49689-2023 artfynd.xlsx
+++ b/artfynd/A 49689-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113201517</v>
+        <v>113201184</v>
       </c>
       <c r="B2" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338715</v>
+        <v>338431</v>
       </c>
       <c r="R2" t="n">
-        <v>6560995</v>
+        <v>6560810</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113201184</v>
+        <v>113201517</v>
       </c>
       <c r="B3" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338431</v>
+        <v>338715</v>
       </c>
       <c r="R3" t="n">
-        <v>6560810</v>
+        <v>6560995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
         <v>113201732</v>
       </c>
       <c r="B4" t="n">
-        <v>96311</v>
+        <v>96315</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 49689-2023 artfynd.xlsx
+++ b/artfynd/A 49689-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113201184</v>
+        <v>113201517</v>
       </c>
       <c r="B2" t="n">
         <v>91344</v>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338431</v>
+        <v>338715</v>
       </c>
       <c r="R2" t="n">
-        <v>6560810</v>
+        <v>6560995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +788,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113201517</v>
+        <v>113201184</v>
       </c>
       <c r="B3" t="n">
         <v>91344</v>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338715</v>
+        <v>338431</v>
       </c>
       <c r="R3" t="n">
-        <v>6560995</v>
+        <v>6560810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49689-2023 artfynd.xlsx
+++ b/artfynd/A 49689-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113201517</v>
+        <v>113201184</v>
       </c>
       <c r="B2" t="n">
-        <v>91344</v>
+        <v>91350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338715</v>
+        <v>338431</v>
       </c>
       <c r="R2" t="n">
-        <v>6560995</v>
+        <v>6560810</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113201184</v>
+        <v>113201732</v>
       </c>
       <c r="B3" t="n">
-        <v>91344</v>
+        <v>96321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338431</v>
+        <v>338771</v>
       </c>
       <c r="R3" t="n">
-        <v>6560810</v>
+        <v>6560994</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113201732</v>
+        <v>113201517</v>
       </c>
       <c r="B4" t="n">
-        <v>96315</v>
+        <v>91350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338771</v>
+        <v>338715</v>
       </c>
       <c r="R4" t="n">
-        <v>6560994</v>
+        <v>6560995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 49689-2023 artfynd.xlsx
+++ b/artfynd/A 49689-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113201184</v>
+        <v>113201517</v>
       </c>
       <c r="B2" t="n">
         <v>91350</v>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338431</v>
+        <v>338715</v>
       </c>
       <c r="R2" t="n">
-        <v>6560810</v>
+        <v>6560995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113201732</v>
+        <v>113201184</v>
       </c>
       <c r="B3" t="n">
-        <v>96321</v>
+        <v>91350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338771</v>
+        <v>338431</v>
       </c>
       <c r="R3" t="n">
-        <v>6560994</v>
+        <v>6560810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113201517</v>
+        <v>113201732</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>96321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338715</v>
+        <v>338771</v>
       </c>
       <c r="R4" t="n">
-        <v>6560995</v>
+        <v>6560994</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 49689-2023 artfynd.xlsx
+++ b/artfynd/A 49689-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49689-2023 artfynd.xlsx
+++ b/artfynd/A 49689-2023 artfynd.xlsx
@@ -675,51 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113201732</v>
+        <v>113201184</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björneberget (Björneberget), Dls</t>
+          <t>Björneberget, Björneberget, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338771</v>
+        <v>338430</v>
       </c>
       <c r="R2" t="n">
-        <v>6560994</v>
+        <v>6560809</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,19 +783,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113201184</v>
+        <v>113201517</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -825,14 +815,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björneberget (Björneberget), Dls</t>
+          <t>Björneberget, Björneberget, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338430</v>
+        <v>338715</v>
       </c>
       <c r="R3" t="n">
-        <v>6560809</v>
+        <v>6560996</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113201517</v>
+        <v>113201732</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,35 +902,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björneberget (Björneberget), Dls</t>
+          <t>Björneberget, Björneberget, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338715</v>
+        <v>338771</v>
       </c>
       <c r="R4" t="n">
-        <v>6560996</v>
+        <v>6560994</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 49689-2023 artfynd.xlsx
+++ b/artfynd/A 49689-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113201184</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113201517</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,8 +1011,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113201732</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>